--- a/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="155">
   <si>
     <t>Property</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T08:55:07+00:00</t>
+    <t>2024-05-03T14:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,7 +83,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Lorsque le corps du CDA est structuré, la métadonnée 'formatCode' provient de l'élément 'templateId' (modèle du document structuré). La correspondance entre templateId et formatCode est assurée par cette table d'association</t>
+    <t>Lorsque le corps du CDA est structuré, la métadonnée 'formatCode' provient de l'élément 'templateId' (modèle du document CDA). La correspondance entre templateId et formatCode est assurée par cette table d'association</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -392,61 +392,61 @@
     <t>urn:ans:ci-sis:bio-ep-bio:2022</t>
   </si>
   <si>
+    <t>1.2.250.1.213.1.1.1.58</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:export-dui:2023</t>
+  </si>
+  <si>
     <t>1.2.250.1.213.1.1.1.56</t>
   </si>
   <si>
     <t>urn:asip:ci-sis:ppp:2023</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.39</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:pre:2010</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.54</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:dis:2010</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.42</t>
+  </si>
+  <si>
+    <t>urn:ihe:eyecare:geneyeevalcn:2014</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.43</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.44</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.45</t>
+  </si>
+  <si>
+    <t>urn:ihe:rad:CDA:ImagingReportStructuredHeadings:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.55</t>
+  </si>
+  <si>
+    <t>urn:ihe:lab:xd-lab:2008</t>
+  </si>
+  <si>
     <t>1.2.250.1.213.1.1.1.57</t>
   </si>
   <si>
     <t>urn:ihe:palm:apsr:2016</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.39</t>
-  </si>
-  <si>
-    <t>urn:ihe:pharm:pre:2010</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.58</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:export-dui:2023</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.54</t>
-  </si>
-  <si>
-    <t>urn:ihe:pharm:dis:2010</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.42</t>
-  </si>
-  <si>
-    <t>urn:ihe:eyecare:geneyeevalcn:2014</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.43</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.44</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.45</t>
-  </si>
-  <si>
-    <t>urn:ihe:rad:CDA:ImagingReportStructuredHeadings:2013</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.55</t>
-  </si>
-  <si>
-    <t>urn:ihe:lab:xd-lab:2008</t>
   </si>
   <si>
     <t>1.3.6.1.4.1.19376.1.3.3</t>
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1491,59 +1491,59 @@
         <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1562,42 +1562,29 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:18:47+00:00</t>
+    <t>2024-05-03T14:27:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:27:04+00:00</t>
+    <t>2024-05-03T14:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:31:09+00:00</t>
+    <t>2024-05-03T15:46:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="197">
   <si>
     <t>Property</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T15:46:37+00:00</t>
+    <t>2024-05-04T12:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -402,6 +402,132 @@
   </si>
   <si>
     <t>urn:asip:ci-sis:ppp:2023</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.1</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:all:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.1</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:breast:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.2</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:colon:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.3</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:prostate:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.4</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:thyroid:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.5</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:lung:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.6</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:skin:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.7</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:kidney:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.8</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:cervix:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.9</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:endometrium:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.10</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:ovary:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.11</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:esophagus:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.12</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:stomach:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.13</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:liver:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.14</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:pancreas:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.15</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:testis:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.16</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:urinary_bladder:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.17</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:lip_oral_cavity:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.18</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:pharynx:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.19</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:salivary_gland:2010</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.8.1.1.2.20</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:larynx:2010</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
@@ -751,7 +877,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1398,6 +1524,279 @@
         <v>128</v>
       </c>
       <c r="E49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D64" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D67" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E70" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1406,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1437,7 +1836,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>
@@ -1445,146 +1844,133 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1615,7 +2001,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>32</v>
@@ -1624,7 +2010,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>
@@ -1632,66 +2018,66 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="E7" s="2"/>
     </row>

--- a/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T12:21:39+00:00</t>
+    <t>2024-05-04T13:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -404,6 +404,60 @@
     <t>urn:asip:ci-sis:ppp:2023</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.39</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:pre:2010</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.54</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:dis:2010</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.42</t>
+  </si>
+  <si>
+    <t>urn:ihe:eyecare:geneyeevalcn:2014</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.43</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.44</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.45</t>
+  </si>
+  <si>
+    <t>urn:ihe:rad:CDA:ImagingReportStructuredHeadings:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.55</t>
+  </si>
+  <si>
+    <t>urn:ihe:lab:xd-lab:2008</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.57</t>
+  </si>
+  <si>
+    <t>urn:ihe:palm:apsr:2016</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.3.3</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.51</t>
+  </si>
+  <si>
+    <t>urn:ihe:pcc:ips:2020</t>
+  </si>
+  <si>
     <t>1.3.6.1.4.1.19376.1.8.1.1.1</t>
   </si>
   <si>
@@ -528,60 +582,6 @@
   </si>
   <si>
     <t>urn:ihe:pat:apsr:larynx:2010</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.39</t>
-  </si>
-  <si>
-    <t>urn:ihe:pharm:pre:2010</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.54</t>
-  </si>
-  <si>
-    <t>urn:ihe:pharm:dis:2010</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.42</t>
-  </si>
-  <si>
-    <t>urn:ihe:eyecare:geneyeevalcn:2014</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.43</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.44</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.45</t>
-  </si>
-  <si>
-    <t>urn:ihe:rad:CDA:ImagingReportStructuredHeadings:2013</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.55</t>
-  </si>
-  <si>
-    <t>urn:ihe:lab:xd-lab:2008</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.57</t>
-  </si>
-  <si>
-    <t>urn:ihe:palm:apsr:2016</t>
-  </si>
-  <si>
-    <t>1.3.6.1.4.1.19376.1.3.3</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.51</t>
-  </si>
-  <si>
-    <t>urn:ihe:pcc:ips:2020</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R221-ModeleDocumentCDANonStructure/FHIR/TRE-R221-ModeleDocumentCDANonStructure</t>
@@ -877,7 +877,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1524,279 +1524,6 @@
         <v>128</v>
       </c>
       <c r="E49" s="2"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B50" s="2"/>
-      <c r="C50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="E50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="B51" s="2"/>
-      <c r="C51" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B52" s="2"/>
-      <c r="C52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E52" s="2"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B53" s="2"/>
-      <c r="C53" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B55" s="2"/>
-      <c r="C55" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D55" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="B56" s="2"/>
-      <c r="C56" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D56" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="E56" s="2"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B57" s="2"/>
-      <c r="C57" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="E57" s="2"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B58" s="2"/>
-      <c r="C58" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D58" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="E58" s="2"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="B59" s="2"/>
-      <c r="C59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D59" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="B60" s="2"/>
-      <c r="C60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D60" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="E60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="B61" s="2"/>
-      <c r="C61" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="E61" s="2"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="B62" s="2"/>
-      <c r="C62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D62" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="E62" s="2"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="B63" s="2"/>
-      <c r="C63" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D63" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="B64" s="2"/>
-      <c r="C64" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D64" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="E64" s="2"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="B65" s="2"/>
-      <c r="C65" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D65" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="E65" s="2"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="B66" s="2"/>
-      <c r="C66" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="E66" s="2"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="B67" s="2"/>
-      <c r="C67" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="B68" s="2"/>
-      <c r="C68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D68" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="E68" s="2"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="B69" s="2"/>
-      <c r="C69" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D69" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="B70" s="2"/>
-      <c r="C70" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D70" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="E70" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1805,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1836,7 +1563,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>
@@ -1844,133 +1571,406 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>186</v>
+        <v>144</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D12" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D33" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E33" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2010,7 +2010,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>

--- a/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T13:53:38+00:00</t>
+    <t>2024-05-04T15:01:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
